--- a/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day3Be.xlsx
+++ b/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day3Be.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Download_Project\Download\Assets\Resources\4. Data\1. VisualNovel\Dialogs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gksk7\Desktop\Download\Download\Assets\Resources\4. Data\1. VisualNovel\Dialogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72777CFF-20ED-4F8B-A9E7-9705CBDCC7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D2D20B-CC3B-4B0A-AD70-5AB6E7BEABF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="760" activeTab="5" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="760" activeTab="5" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
   </bookViews>
   <sheets>
     <sheet name="S00_1_Road" sheetId="2" r:id="rId1"/>
@@ -2001,22 +2001,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2492B5-5286-4C51-A0EE-617DAAF7402C}">
   <dimension ref="A1:R67"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" customWidth="1"/>
-    <col min="3" max="3" width="9.8984375" customWidth="1"/>
-    <col min="4" max="4" width="7.19921875" customWidth="1"/>
-    <col min="5" max="5" width="18.19921875" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="7.25" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="6" width="72.5" customWidth="1"/>
-    <col min="7" max="7" width="24.3984375" customWidth="1"/>
-    <col min="9" max="9" width="24.3984375" customWidth="1"/>
+    <col min="7" max="7" width="24.375" customWidth="1"/>
+    <col min="9" max="9" width="24.375" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" customWidth="1"/>
-    <col min="12" max="12" width="13.69921875" customWidth="1"/>
-    <col min="13" max="13" width="12.69921875" customWidth="1"/>
-    <col min="14" max="14" width="14.19921875" customWidth="1"/>
-    <col min="15" max="15" width="16.3984375" customWidth="1"/>
-    <col min="16" max="16" width="15.69921875" customWidth="1"/>
+    <col min="11" max="11" width="9.75" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="12.75" customWidth="1"/>
+    <col min="14" max="14" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="16.375" customWidth="1"/>
+    <col min="16" max="16" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="25.95" customHeight="1">
+    <row r="3" spans="1:18" ht="25.9" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="31.2" customHeight="1">
+    <row r="4" spans="1:18" ht="31.15" customHeight="1">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="25.95" customHeight="1">
+    <row r="5" spans="1:18" ht="25.9" customHeight="1">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="28.2" customHeight="1">
+    <row r="8" spans="1:18" ht="28.15" customHeight="1">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2748,18 +2748,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415DC7F1-5C60-420E-8CE5-E5358336FABA}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="5" max="5" width="17.69921875" customWidth="1"/>
-    <col min="6" max="6" width="69.8984375" customWidth="1"/>
+    <col min="5" max="5" width="17.75" customWidth="1"/>
+    <col min="6" max="6" width="69.875" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="21.5" customWidth="1"/>
     <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="12" max="12" width="10.19921875" customWidth="1"/>
-    <col min="13" max="13" width="15.19921875" customWidth="1"/>
+    <col min="12" max="12" width="10.25" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
     <col min="14" max="14" width="39.5" customWidth="1"/>
     <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="15.19921875" customWidth="1"/>
+    <col min="16" max="16" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -3476,12 +3476,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08063B42-9FFB-4627-AE34-3D3DC97935FA}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="5" max="5" width="15.3984375" customWidth="1"/>
-    <col min="6" max="6" width="33.3984375" customWidth="1"/>
-    <col min="7" max="7" width="21.19921875" customWidth="1"/>
-    <col min="10" max="10" width="14.59765625" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="33.375" customWidth="1"/>
+    <col min="7" max="7" width="21.25" customWidth="1"/>
+    <col min="10" max="10" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -3616,12 +3616,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAFCA4D8-53B5-40C3-B1B4-7A126FDAA54C}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="36.19921875" customWidth="1"/>
-    <col min="7" max="7" width="18.19921875" customWidth="1"/>
-    <col min="10" max="10" width="23.09765625" customWidth="1"/>
+    <col min="6" max="6" width="36.25" customWidth="1"/>
+    <col min="7" max="7" width="18.25" customWidth="1"/>
+    <col min="10" max="10" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -3756,12 +3756,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BDC7567-CEFB-4428-8A63-E09991D123C9}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="5" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="33.09765625" customWidth="1"/>
-    <col min="7" max="7" width="17.8984375" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="33.125" customWidth="1"/>
+    <col min="7" max="7" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -3896,13 +3896,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3077775-3632-4DC2-AD34-ED15BB71D914}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="5" max="5" width="14.09765625" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="58" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" customWidth="1"/>
-    <col min="8" max="8" width="18.59765625" customWidth="1"/>
-    <col min="10" max="10" width="18.59765625" customWidth="1"/>
+    <col min="7" max="7" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="18.625" customWidth="1"/>
+    <col min="10" max="10" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
